--- a/fixes/Intune_Bugs.xlsx
+++ b/fixes/Intune_Bugs.xlsx
@@ -10,6 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bug Registry" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Examples" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="How to Reproduce" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sales Talk Track" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Bug Registry'!$A$2:$M$2</definedName>
@@ -110,7 +111,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="15">
+  <fills count="16">
     <fill>
       <patternFill/>
     </fill>
@@ -182,6 +183,11 @@
         <fgColor rgb="001E272E"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF3CD"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -209,7 +215,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -326,6 +332,47 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2676,4 +2723,457 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="001B5E20"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B40"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="43" t="inlineStr">
+        <is>
+          <t>SALES TALK TRACK  ·  Microsoft Intune  ·  Asset of Interest — Noncompliant Devices  ·  Updated 2026-07-04</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="44" t="inlineStr">
+        <is>
+          <t>STATUS: PARTIAL DEMO  —  Section A is live today. Section B is blocked by UAI connector bugs. Section C is the future story once bugs are resolved.</t>
+        </is>
+      </c>
+      <c r="B2" s="45" t="n"/>
+    </row>
+    <row r="3" ht="28" customHeight="1">
+      <c r="A3" s="38" t="inlineStr">
+        <is>
+          <t>Audience</t>
+        </is>
+      </c>
+      <c r="B3" s="39" t="inlineStr">
+        <is>
+          <t>Security architects, IT operations leads, risk/compliance owners.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="38" t="inlineStr">
+        <is>
+          <t>Duration</t>
+        </is>
+      </c>
+      <c r="B4" s="39" t="inlineStr">
+        <is>
+          <t>6–10 min (Section A only, today). Grows to 15–20 min once UAI connector is fixed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="6" customHeight="1">
+      <c r="A5" s="34" t="n"/>
+      <c r="B5" s="34" t="n"/>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="46" t="inlineStr">
+        <is>
+          <t>PRE-DEMO SETUP</t>
+        </is>
+      </c>
+      <c r="B6" s="47" t="n"/>
+    </row>
+    <row r="7" ht="72" customHeight="1">
+      <c r="A7" s="38" t="inlineStr">
+        <is>
+          <t>Setup steps</t>
+        </is>
+      </c>
+      <c r="B7" s="39" t="inlineStr">
+        <is>
+          <t>1. Autowire → Microsoft Intune in Mock Deployer → confirm MicrosoftIntune_Job last synced &lt; 2 hrs
+2. UAI → Assets → confirm 763 Intune devices visible
+3. Filter compliance state = noncompliant → confirm ~62 devices
+4. Open one device Properties → confirm partner_reported_threat_state field is visible</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="80" customHeight="1">
+      <c r="A8" s="48" t="inlineStr">
+        <is>
+          <t>⚠️  BEFORE YOU START — READ THIS</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>IP Address / Location / Region are BLANK for ALL Intune assets. This is BUG-001 in this workbook.
+UAI does not store the MAC address even though it fetches it.
+Do NOT say 'let me show you where this device is on the network' — it will show blank and kill the story.
+The demo works on compliance state + threat signal today. Network location is the future story (Section C).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="6" customHeight="1">
+      <c r="A9" s="34" t="n"/>
+      <c r="B9" s="34" t="n"/>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="49" t="inlineStr">
+        <is>
+          <t>SECTION A  —  WHAT YOU CAN DEMO TODAY</t>
+        </is>
+      </c>
+      <c r="B10" s="27" t="n"/>
+    </row>
+    <row r="11" ht="120" customHeight="1">
+      <c r="A11" s="50" t="inlineStr">
+        <is>
+          <t>STEP 1  ·  Set the scene</t>
+        </is>
+      </c>
+      <c r="B11" s="28" t="inlineStr">
+        <is>
+          <t>UAI → Asset Insights → Assets. Show the full fleet: 763 Microsoft Intune-managed devices.
+Say:
+"Every one of these devices is enrolled in your MDM. Intune tracks their compliance state. UAI takes that signal and puts it on the same canvas as your network and endpoint tools. Let me show you what that looks like for devices that are actively violating policy."</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="120" customHeight="1">
+      <c r="A12" s="50" t="inlineStr">
+        <is>
+          <t>STEP 2  ·  Surface noncompliant devices</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Filter: complianceState = noncompliant → 62 devices appear.
+Say:
+"62 devices — 8% of your managed fleet — are actively out of MDM policy right now. You can see immediately: Windows laptops, VDI machines, Android phones. Same compliance failure, very different risk profiles."</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="120" customHeight="1">
+      <c r="A13" s="50" t="inlineStr">
+        <is>
+          <t>STEP 3  ·  Grace period urgency</t>
+        </is>
+      </c>
+      <c r="B13" s="51" t="inlineStr">
+        <is>
+          <t>Change filter: complianceState = inGracePeriod → 62 more devices.
+Highlight: lsys-sgp-lap-0018 / lsys-nyc-lap-0360 / lsys-sfo-and-1435 — grace period expires TODAY.
+Say:
+"These 62 aren't blocked yet — but they're on a countdown. Three of them expire today. After that, depending on your Conditional Access config, they lose access to corporate resources. UAI surfaces this before Intune sends an alert."</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="120" customHeight="1">
+      <c r="A14" s="50" t="inlineStr">
+        <is>
+          <t>STEP 4  ·  CrowdStrike cross-vendor correlation</t>
+        </is>
+      </c>
+      <c r="B14" s="12" t="inlineStr">
+        <is>
+          <t>Click into any noncompliant Windows laptop → Sources section.
+Show it is correlated with CrowdStrike Falcon.
+Say:
+"44 of these 62 noncompliant Windows devices also appear in CrowdStrike Falcon. UAI correlates both sources on a single asset record — you don't chase the same device across two different consoles. Intune says it's out of policy. CrowdStrike shows its threat posture. One place."</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="120" customHeight="1">
+      <c r="A15" s="50" t="inlineStr">
+        <is>
+          <t>STEP 5  ·  Threat signal (what DOES work from enrichment)</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>Open a noncompliant Windows device → Properties → find partner_reported_threat_state.
+Show: 'unknown'
+Then open a compliant Windows device → same field.
+Show: 'secure'
+Say:
+"Compliant devices — with CrowdStrike running cleanly — show 'secure'. Noncompliant devices show 'unknown'. That means the EDR signal has gone dark. Out of policy AND the endpoint protection reporting has stopped. That's a compounding risk, not just a policy checkbox."</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="120" customHeight="1">
+      <c r="A16" s="50" t="inlineStr">
+        <is>
+          <t>STEP 6  ·  VDI anomaly</t>
+        </is>
+      </c>
+      <c r="B16" s="12" t="inlineStr">
+        <is>
+          <t>Search hostname: lsys-lon-vdi-0929 or lsys-sfo-vdi-0904.
+Say:
+"VDI machines failing compliance is a different level of risk. These are shared infrastructure endpoints — every session running on this image inherits this compliance state. That's not a user problem. That's an infrastructure problem."</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="6" customHeight="1">
+      <c r="A17" s="34" t="n"/>
+      <c r="B17" s="34" t="n"/>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="46" t="inlineStr">
+        <is>
+          <t>DISCOVERY QUESTIONS</t>
+        </is>
+      </c>
+      <c r="B18" s="47" t="n"/>
+    </row>
+    <row r="19" ht="70" customHeight="1">
+      <c r="A19" s="38" t="inlineStr">
+        <is>
+          <t>Questions</t>
+        </is>
+      </c>
+      <c r="B19" s="39" t="inlineStr">
+        <is>
+          <t>1.  "How do you currently know which noncompliant Intune devices are actively being used — not just enrolled?"
+2.  "When a grace period expires, how fast does your team find the device on the network?"
+3.  "If a device is noncompliant AND its EDR agent goes silent — what's your detection time?"</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="46" t="inlineStr">
+        <is>
+          <t>OBJECTIONS</t>
+        </is>
+      </c>
+      <c r="B20" s="47" t="n"/>
+    </row>
+    <row r="21" ht="52" customHeight="1">
+      <c r="A21" s="38" t="inlineStr">
+        <is>
+          <t>"We have Intune Conditional Access"</t>
+        </is>
+      </c>
+      <c r="B21" s="39" t="inlineStr">
+        <is>
+          <t>"Conditional Access enforces policy — it blocks or allows. UAI enriches context — it tells you WHICH devices are affected, WHAT other tools see them, and HOW LONG they've been in that state. Different jobs."</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="48" customHeight="1">
+      <c r="A22" s="38" t="inlineStr">
+        <is>
+          <t>"Can't we pull this from SIEM?"</t>
+        </is>
+      </c>
+      <c r="B22" s="39" t="inlineStr">
+        <is>
+          <t>"SIEM aggregates events after they happen. UAI maintains a live asset inventory — compliance state, threat signal, sync timestamps — updated on every Intune poll. No correlation query needed."</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="60" customHeight="1">
+      <c r="A23" s="52" t="inlineStr">
+        <is>
+          <t>"IP and location are blank"</t>
+        </is>
+      </c>
+      <c r="B23" s="53" t="inlineStr">
+        <is>
+          <t>"Good catch — that's a known connector issue we're actively tracking (BUG-001 in our bug registry). The mock returns correct MAC data; UAI's Intune connector isn't storing it yet. Once fixed, every Intune asset gets IP and location from MAC-to-DHCP correlation. That's when Section C of this talk track goes live."</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="6" customHeight="1">
+      <c r="A24" s="34" t="n"/>
+      <c r="B24" s="34" t="n"/>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="54" t="inlineStr">
+        <is>
+          <t>SECTION B  —  WHAT IS NOT POSSIBLE TODAY  (do not attempt — will show blank)</t>
+        </is>
+      </c>
+      <c r="B25" s="45" t="n"/>
+    </row>
+    <row r="26" ht="60" customHeight="1">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>IP Address / Location / Region
+BUG-001 (High)</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>MAC not stored by UAI → no DHCP correlation → blank IP, Location, Region for all 763 Intune assets.
+Do not navigate to any location-related field during the demo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="60" customHeight="1">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>WHY the device is noncompliant
+BUG-003 (High)</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>deviceHealthAttestationState (BitLocker status, Secure Boot, TPM version) is fetched but discarded. UAI shows 'noncompliant' with zero explanation. Do not try to open attestation details.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="60" customHeight="1">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Enrollment profile (corp vs BYOD detail)
+BUG-004 (Medium)</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>enrollmentProfileName fetched but stored as empty string. Cannot differentiate Autopilot profiles.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="60" customHeight="1">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>MDM cert expiry
+BUG-005 (Medium)</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>managementCertificateExpirationDate fetched but stored as null. Proactive cert alert story not available.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="60" customHeight="1">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>RAM / Memory
+BUG-002 (Medium)</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>physicalMemoryInBytes stored as '0'. Do not reference hardware specs in the demo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="6" customHeight="1">
+      <c r="A31" s="34" t="n"/>
+      <c r="B31" s="34" t="n"/>
+    </row>
+    <row r="32" ht="22" customHeight="1">
+      <c r="A32" s="55" t="inlineStr">
+        <is>
+          <t>SECTION C  —  WHAT BECOMES POSSIBLE ONCE UAI FIXES THE CONNECTOR</t>
+        </is>
+      </c>
+      <c r="B32" s="18" t="n"/>
+    </row>
+    <row r="33" ht="36" customHeight="1">
+      <c r="A33" s="38" t="inlineStr">
+        <is>
+          <t>Context</t>
+        </is>
+      </c>
+      <c r="B33" s="28" t="inlineStr">
+        <is>
+          <t>All data below is already in the mock and correct. The moment UAI fixes its connector mapping, these demo angles go live with zero mock changes needed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="90" customHeight="1">
+      <c r="A34" s="56" t="inlineStr">
+        <is>
+          <t>Network location  (after BUG-001 fix)</t>
+        </is>
+      </c>
+      <c r="B34" s="28" t="inlineStr">
+        <is>
+          <t>Show noncompliant devices on a map with real IP addresses and site locations.
+Say: "This device is noncompliant AND it's on subnet 10.22.4.0/24 in the Singapore office. Your network team can isolate it in minutes."</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="90" customHeight="1">
+      <c r="A35" s="56" t="inlineStr">
+        <is>
+          <t>Root cause of noncompliance  (after BUG-003 fix)</t>
+        </is>
+      </c>
+      <c r="B35" s="28" t="inlineStr">
+        <is>
+          <t>Open a noncompliant device → deviceHealthAttestationState:
+  bitLockerStatus: PROTECTION_OFF  →  disk is not encrypted
+  secureBoot: disabled             →  BIOS does not enforce trusted boot
+  tpmVersion: 1.2                  →  TPM chip too old for Windows 11 requirements
+Say: "UAI doesn't just tell you the device is out of policy — it tells you exactly why, without opening Intune."</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="90" customHeight="1">
+      <c r="A36" s="56" t="inlineStr">
+        <is>
+          <t>Proactive MDM cert management  (after BUG-005 fix)</t>
+        </is>
+      </c>
+      <c r="B36" s="28" t="inlineStr">
+        <is>
+          <t>Filter: managementCertificateExpirationDate within next 30 days.
+Say: "Before UAI, finding devices about to lose MDM control required a PowerShell script or an Intune report. Here it's a one-click filter across your entire fleet — before they drop off."</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="90" customHeight="1">
+      <c r="A37" s="56" t="inlineStr">
+        <is>
+          <t>Corp vs BYOD risk segmentation  (after BUG-004 fix)</t>
+        </is>
+      </c>
+      <c r="B37" s="28" t="inlineStr">
+        <is>
+          <t>Filter noncompliant BYOD-enrolled devices vs corporate Autopilot devices separately.
+Different remediation paths, different risk owners, different escalation paths.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="6" customHeight="1">
+      <c r="A38" s="34" t="n"/>
+      <c r="B38" s="34" t="n"/>
+    </row>
+    <row r="39" ht="22" customHeight="1">
+      <c r="A39" s="57" t="inlineStr">
+        <is>
+          <t>CLOSE</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="n"/>
+    </row>
+    <row r="40" ht="90" customHeight="1">
+      <c r="A40" s="38" t="inlineStr">
+        <is>
+          <t>Close line</t>
+        </is>
+      </c>
+      <c r="B40" s="12" t="inlineStr">
+        <is>
+          <t>"What you saw today is Infoblox taking your existing Intune compliance data and surfacing it as a network risk signal. 62 noncompliant devices, 44 of them visible in CrowdStrike, 3 grace periods expiring today, and the EDR signal dark on every single one. That's not just an MDM report — that's a network and endpoint risk picture in one place. And when the connector is fully enriched, we add location, root cause, and proactive cert management on top of that."</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/fixes/Intune_Bugs.xlsx
+++ b/fixes/Intune_Bugs.xlsx
@@ -11,6 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Examples" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="How to Reproduce" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sales Talk Track" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Customer Use Cases" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Bug Registry'!$A$2:$M$2</definedName>
@@ -22,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="15">
+  <fonts count="16">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -110,8 +111,13 @@
       <color rgb="00A5D6A7"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="16">
+  <fills count="17">
     <fill>
       <patternFill/>
     </fill>
@@ -188,6 +194,11 @@
         <fgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E0F2F1"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -215,7 +226,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -373,6 +384,24 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3176,4 +3205,633 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="004A0072"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="43" t="inlineStr">
+        <is>
+          <t>CUSTOMER USE CASES  ·  Microsoft Intune + UAI (Asset Insights)  ·  Draft 2026-07-04</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
+    </row>
+    <row r="2" ht="36" customHeight="1">
+      <c r="A2" s="58" t="inlineStr">
+        <is>
+          <t>What real customer problems does the Intune + UAI integration solve?  Section A = available today.  Section B = unlocked once UAI connector bugs are fixed (no mock changes needed).</t>
+        </is>
+      </c>
+      <c r="B2" s="16" t="n"/>
+      <c r="C2" s="16" t="n"/>
+      <c r="D2" s="16" t="n"/>
+      <c r="E2" s="16" t="n"/>
+      <c r="F2" s="16" t="n"/>
+      <c r="G2" s="16" t="n"/>
+    </row>
+    <row r="3" ht="36" customHeight="1">
+      <c r="A3" s="59" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B3" s="59" t="inlineStr">
+        <is>
+          <t>Use Case</t>
+        </is>
+      </c>
+      <c r="C3" s="59" t="inlineStr">
+        <is>
+          <t>Customer Problem</t>
+        </is>
+      </c>
+      <c r="D3" s="59" t="inlineStr">
+        <is>
+          <t>What UAI Adds</t>
+        </is>
+      </c>
+      <c r="E3" s="59" t="inlineStr">
+        <is>
+          <t>Customer Question Answered</t>
+        </is>
+      </c>
+      <c r="F3" s="59" t="inlineStr">
+        <is>
+          <t>Today?</t>
+        </is>
+      </c>
+      <c r="G3" s="59" t="inlineStr">
+        <is>
+          <t>Blocker</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="49" t="inlineStr">
+        <is>
+          <t>SECTION A  —  AVAILABLE TODAY</t>
+        </is>
+      </c>
+      <c r="B4" s="27" t="n"/>
+      <c r="C4" s="27" t="n"/>
+      <c r="D4" s="27" t="n"/>
+      <c r="E4" s="27" t="n"/>
+      <c r="F4" s="27" t="n"/>
+      <c r="G4" s="27" t="n"/>
+    </row>
+    <row r="5" ht="95" customHeight="1">
+      <c r="A5" s="60" t="inlineStr">
+        <is>
+          <t>UC-1</t>
+        </is>
+      </c>
+      <c r="B5" s="28" t="inlineStr">
+        <is>
+          <t>MDM Compliance Visibility
+across the full fleet</t>
+        </is>
+      </c>
+      <c r="C5" s="28" t="inlineStr">
+        <is>
+          <t>Security teams know Intune flags noncompliant devices but can't quickly answer: how many, what type, which site?</t>
+        </is>
+      </c>
+      <c r="D5" s="28" t="inlineStr">
+        <is>
+          <t>Single view of 763 devices with live compliance state.
+Filter: 62 noncompliant (8%), 62 grace (8%), 639 compliant (84%).
+Device category: laptop / VDI / Android, corp vs BYOD.</t>
+        </is>
+      </c>
+      <c r="E5" s="28" t="inlineStr">
+        <is>
+          <t>"How many of our enrolled devices are actively out of policy right now?"</t>
+        </is>
+      </c>
+      <c r="F5" s="28" t="inlineStr">
+        <is>
+          <t>✅  YES</t>
+        </is>
+      </c>
+      <c r="G5" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="95" customHeight="1">
+      <c r="A6" s="60" t="inlineStr">
+        <is>
+          <t>UC-2</t>
+        </is>
+      </c>
+      <c r="B6" s="28" t="inlineStr">
+        <is>
+          <t>Grace Period Deadline
+Tracking</t>
+        </is>
+      </c>
+      <c r="C6" s="28" t="inlineStr">
+        <is>
+          <t>IT teams miss grace period expiry. Devices silently lose access. No live operational view in Intune.</t>
+        </is>
+      </c>
+      <c r="D6" s="28" t="inlineStr">
+        <is>
+          <t>62 inGracePeriod devices in one filter. 3 expire TODAY.
+compliance_grace_period_expiration_date_time shown per device.</t>
+        </is>
+      </c>
+      <c r="E6" s="28" t="inlineStr">
+        <is>
+          <t>"Which devices will lose MDM compliance in the next 24–72 hours?"</t>
+        </is>
+      </c>
+      <c r="F6" s="28" t="inlineStr">
+        <is>
+          <t>✅  YES</t>
+        </is>
+      </c>
+      <c r="G6" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="95" customHeight="1">
+      <c r="A7" s="60" t="inlineStr">
+        <is>
+          <t>UC-3</t>
+        </is>
+      </c>
+      <c r="B7" s="28" t="inlineStr">
+        <is>
+          <t>Cross-vendor Risk Correlation
+Intune + CrowdStrike Falcon</t>
+        </is>
+      </c>
+      <c r="C7" s="28" t="inlineStr">
+        <is>
+          <t>MDM noncompliance and EDR threat posture tracked in separate consoles. Manual cross-reference.</t>
+        </is>
+      </c>
+      <c r="D7" s="28" t="inlineStr">
+        <is>
+          <t>44 noncompliant Windows devices correlated across Intune + CrowdStrike in one record.
+partner_reported_threat_state: compliant → 'secure', noncompliant → 'unknown'.</t>
+        </is>
+      </c>
+      <c r="E7" s="28" t="inlineStr">
+        <is>
+          <t>"Which noncompliant devices also have a degraded or missing EDR signal?"</t>
+        </is>
+      </c>
+      <c r="F7" s="28" t="inlineStr">
+        <is>
+          <t>✅  YES</t>
+        </is>
+      </c>
+      <c r="G7" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="95" customHeight="1">
+      <c r="A8" s="60" t="inlineStr">
+        <is>
+          <t>UC-4</t>
+        </is>
+      </c>
+      <c r="B8" s="28" t="inlineStr">
+        <is>
+          <t>VDI / Shared Infrastructure
+Compliance Risk</t>
+        </is>
+      </c>
+      <c r="C8" s="28" t="inlineStr">
+        <is>
+          <t>VDI noncompliance affects every session user. Most tools treat it identically to a laptop.</t>
+        </is>
+      </c>
+      <c r="D8" s="28" t="inlineStr">
+        <is>
+          <t>40 VDI devices filterable separately.
+Noncompliant VDI flagged: lsys-lon-vdi-0929, lsys-sfo-vdi-0904.
+Device category 'Corporate' visible immediately.</t>
+        </is>
+      </c>
+      <c r="E8" s="28" t="inlineStr">
+        <is>
+          <t>"Are any shared VDI machines out of compliance — and how many users are exposed?"</t>
+        </is>
+      </c>
+      <c r="F8" s="28" t="inlineStr">
+        <is>
+          <t>✅  YES</t>
+        </is>
+      </c>
+      <c r="G8" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="95" customHeight="1">
+      <c r="A9" s="60" t="inlineStr">
+        <is>
+          <t>UC-5</t>
+        </is>
+      </c>
+      <c r="B9" s="28" t="inlineStr">
+        <is>
+          <t>BYOD Risk Segmentation</t>
+        </is>
+      </c>
+      <c r="C9" s="28" t="inlineStr">
+        <is>
+          <t>BYOD devices enrolled in Intune treated identically to corporate laptops. Risk posture is fundamentally different.</t>
+        </is>
+      </c>
+      <c r="D9" s="28" t="inlineStr">
+        <is>
+          <t>managedDeviceOwnerType = 'personal' visible (68 BYOD Android).
+Noncompliant BYOD threat state = 'unknown' (no CrowdStrike on personal).
+Enrollment type separates BYOD from corp.</t>
+        </is>
+      </c>
+      <c r="E9" s="28" t="inlineStr">
+        <is>
+          <t>"Which noncompliant devices are BYOD vs corporate — and does that change our response?"</t>
+        </is>
+      </c>
+      <c r="F9" s="28" t="inlineStr">
+        <is>
+          <t>✅  YES</t>
+        </is>
+      </c>
+      <c r="G9" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="6" customHeight="1">
+      <c r="A10" s="34" t="n"/>
+      <c r="B10" s="34" t="n"/>
+      <c r="C10" s="34" t="n"/>
+      <c r="D10" s="34" t="n"/>
+      <c r="E10" s="34" t="n"/>
+      <c r="F10" s="34" t="n"/>
+      <c r="G10" s="34" t="n"/>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="55" t="inlineStr">
+        <is>
+          <t>SECTION B  —  UNLOCKED ONCE UAI CONNECTOR BUGS ARE FIXED  (mock data already correct)</t>
+        </is>
+      </c>
+      <c r="B11" s="18" t="n"/>
+      <c r="C11" s="18" t="n"/>
+      <c r="D11" s="18" t="n"/>
+      <c r="E11" s="18" t="n"/>
+      <c r="F11" s="18" t="n"/>
+      <c r="G11" s="18" t="n"/>
+    </row>
+    <row r="12" ht="95" customHeight="1">
+      <c r="A12" s="61" t="inlineStr">
+        <is>
+          <t>UC-6</t>
+        </is>
+      </c>
+      <c r="B12" s="62" t="inlineStr">
+        <is>
+          <t>Network Location of
+Noncompliant Devices</t>
+        </is>
+      </c>
+      <c r="C12" s="62" t="inlineStr">
+        <is>
+          <t>Security knows a device is noncompliant but can't find it on the network without manual DHCP lookups.</t>
+        </is>
+      </c>
+      <c r="D12" s="62" t="inlineStr">
+        <is>
+          <t>wiFiMacAddress stored → DHCP/IPAM correlation → real IP + Location + Region.
+Network Last Seen: is device currently active?</t>
+        </is>
+      </c>
+      <c r="E12" s="62" t="inlineStr">
+        <is>
+          <t>"Where on the network is this noncompliant device right now?"</t>
+        </is>
+      </c>
+      <c r="F12" s="20" t="inlineStr">
+        <is>
+          <t>❌  NOT YET</t>
+        </is>
+      </c>
+      <c r="G12" s="20" t="inlineStr">
+        <is>
+          <t>BUG-001
+wiFiMacAddress
+not stored</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="95" customHeight="1">
+      <c r="A13" s="61" t="inlineStr">
+        <is>
+          <t>UC-7</t>
+        </is>
+      </c>
+      <c r="B13" s="62" t="inlineStr">
+        <is>
+          <t>Root Cause of
+Noncompliance</t>
+        </is>
+      </c>
+      <c r="C13" s="62" t="inlineStr">
+        <is>
+          <t>Intune shows 'noncompliant' but gives a long list of possible reasons. Finding the failure needs per-policy drilling.</t>
+        </is>
+      </c>
+      <c r="D13" s="62" t="inlineStr">
+        <is>
+          <t>deviceHealthAttestationState: bitLockerStatus, secureBoot, tpmVersion, healthStatusMismatchInfo per device.</t>
+        </is>
+      </c>
+      <c r="E13" s="62" t="inlineStr">
+        <is>
+          <t>"Why exactly is this device noncompliant — BitLocker, Secure Boot, or TPM?"</t>
+        </is>
+      </c>
+      <c r="F13" s="20" t="inlineStr">
+        <is>
+          <t>❌  NOT YET</t>
+        </is>
+      </c>
+      <c r="G13" s="20" t="inlineStr">
+        <is>
+          <t>BUG-003
+healthAttestation
+not stored</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="95" customHeight="1">
+      <c r="A14" s="61" t="inlineStr">
+        <is>
+          <t>UC-8</t>
+        </is>
+      </c>
+      <c r="B14" s="62" t="inlineStr">
+        <is>
+          <t>Proactive MDM Cert
+Expiry Management</t>
+        </is>
+      </c>
+      <c r="C14" s="62" t="inlineStr">
+        <is>
+          <t>MDM certs expire silently. Devices fall off Intune management. Discovered only when the user calls IT.</t>
+        </is>
+      </c>
+      <c r="D14" s="62" t="inlineStr">
+        <is>
+          <t>managementCertificateExpirationDate per device.
+Filter: expiring in 30 / 60 / 90 days.</t>
+        </is>
+      </c>
+      <c r="E14" s="62" t="inlineStr">
+        <is>
+          <t>"Which managed devices will lose their MDM cert in the next 30 days?"</t>
+        </is>
+      </c>
+      <c r="F14" s="20" t="inlineStr">
+        <is>
+          <t>❌  NOT YET</t>
+        </is>
+      </c>
+      <c r="G14" s="20" t="inlineStr">
+        <is>
+          <t>BUG-005
+certExpiry
+not stored</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="95" customHeight="1">
+      <c r="A15" s="61" t="inlineStr">
+        <is>
+          <t>UC-9</t>
+        </is>
+      </c>
+      <c r="B15" s="62" t="inlineStr">
+        <is>
+          <t>Enrollment Profile
+Audit &amp; Hygiene</t>
+        </is>
+      </c>
+      <c r="C15" s="62" t="inlineStr">
+        <is>
+          <t>Devices land on wrong Autopilot profile. Corp enrolled as BYOD or vice versa. Hard to detect at scale.</t>
+        </is>
+      </c>
+      <c r="D15" s="62" t="inlineStr">
+        <is>
+          <t>enrollmentProfileName per device: Corporate, VDI, Android-BYOD.
+Cross-filter: noncompliant AND profile = Corporate.</t>
+        </is>
+      </c>
+      <c r="E15" s="62" t="inlineStr">
+        <is>
+          <t>"Are BYOD profiles accidentally applied to corporate hardware?"</t>
+        </is>
+      </c>
+      <c r="F15" s="20" t="inlineStr">
+        <is>
+          <t>❌  NOT YET</t>
+        </is>
+      </c>
+      <c r="G15" s="20" t="inlineStr">
+        <is>
+          <t>BUG-004
+enrollmentProfile
+not stored</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="6" customHeight="1">
+      <c r="A16" s="34" t="n"/>
+      <c r="B16" s="34" t="n"/>
+      <c r="C16" s="34" t="n"/>
+      <c r="D16" s="34" t="n"/>
+      <c r="E16" s="34" t="n"/>
+      <c r="F16" s="34" t="n"/>
+      <c r="G16" s="34" t="n"/>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="46" t="inlineStr">
+        <is>
+          <t>QUALIFICATION GUIDE</t>
+        </is>
+      </c>
+      <c r="B17" s="47" t="n"/>
+      <c r="C17" s="47" t="n"/>
+      <c r="D17" s="47" t="n"/>
+      <c r="E17" s="47" t="n"/>
+      <c r="F17" s="47" t="n"/>
+      <c r="G17" s="47" t="n"/>
+    </row>
+    <row r="18" ht="28" customHeight="1">
+      <c r="A18" s="63" t="inlineStr">
+        <is>
+          <t>Persona</t>
+        </is>
+      </c>
+      <c r="B18" s="63" t="inlineStr">
+        <is>
+          <t>Primary Use Cases</t>
+        </is>
+      </c>
+      <c r="C18" s="63" t="inlineStr">
+        <is>
+          <t>Strong Fit Signal</t>
+        </is>
+      </c>
+      <c r="D18" s="63" t="inlineStr">
+        <is>
+          <t>Weak Fit Signal</t>
+        </is>
+      </c>
+      <c r="E18" s="63" t="inlineStr"/>
+      <c r="F18" s="63" t="inlineStr"/>
+      <c r="G18" s="63" t="inlineStr"/>
+    </row>
+    <row r="19" ht="55" customHeight="1">
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>IT Security / SecOps</t>
+        </is>
+      </c>
+      <c r="B19" s="12" t="inlineStr">
+        <is>
+          <t>UC-1, UC-3, UC-7</t>
+        </is>
+      </c>
+      <c r="C19" s="28" t="inlineStr">
+        <is>
+          <t>Intune + CrowdStrike deployed; had incidents from noncompliant devices</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>All-in on Microsoft Defender — cross-vendor story weaker</t>
+        </is>
+      </c>
+      <c r="E19" s="39" t="inlineStr"/>
+      <c r="F19" s="39" t="inlineStr"/>
+      <c r="G19" s="39" t="inlineStr"/>
+    </row>
+    <row r="20" ht="55" customHeight="1">
+      <c r="A20" s="12" t="inlineStr">
+        <is>
+          <t>IT Ops / MDM Admins</t>
+        </is>
+      </c>
+      <c r="B20" s="12" t="inlineStr">
+        <is>
+          <t>UC-2, UC-5, UC-8, UC-9</t>
+        </is>
+      </c>
+      <c r="C20" s="28" t="inlineStr">
+        <is>
+          <t>Missed grace period expirations; BYOD + corp mix in fleet</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>Intune only, no EDR deployed</t>
+        </is>
+      </c>
+      <c r="E20" s="39" t="inlineStr"/>
+      <c r="F20" s="39" t="inlineStr"/>
+      <c r="G20" s="39" t="inlineStr"/>
+    </row>
+    <row r="21" ht="55" customHeight="1">
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>Network / Infrastructure</t>
+        </is>
+      </c>
+      <c r="B21" s="12" t="inlineStr">
+        <is>
+          <t>UC-6</t>
+        </is>
+      </c>
+      <c r="C21" s="28" t="inlineStr">
+        <is>
+          <t>On-prem DHCP/IPAM; needs to locate flagged devices on network</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>Cloud-only org — no DHCP to correlate against</t>
+        </is>
+      </c>
+      <c r="E21" s="39" t="inlineStr"/>
+      <c r="F21" s="39" t="inlineStr"/>
+      <c r="G21" s="39" t="inlineStr"/>
+    </row>
+    <row r="22" ht="55" customHeight="1">
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t>Risk / Compliance</t>
+        </is>
+      </c>
+      <c r="B22" s="12" t="inlineStr">
+        <is>
+          <t>UC-1, UC-4</t>
+        </is>
+      </c>
+      <c r="C22" s="28" t="inlineStr">
+        <is>
+          <t>Fleet compliance rate needed for audit; VDI environment in scope</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>MDM compliance reported separately from risk dashboard</t>
+        </is>
+      </c>
+      <c r="E22" s="39" t="inlineStr"/>
+      <c r="F22" s="39" t="inlineStr"/>
+      <c r="G22" s="39" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>